--- a/proyFinal/src/datos/plantilla_de_estadisticas.xlsx
+++ b/proyFinal/src/datos/plantilla_de_estadisticas.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizas\proyectoFinal\proyFinal\src\datos\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABF614A-933D-47C2-B36D-F8C7F00AE307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>ESTADISTICA INDIVIDUAL DE JUEGO</t>
   </si>
@@ -106,39 +115,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="14"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -149,7 +140,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -160,7 +151,7 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="8"/>
       <color indexed="8"/>
       <name val="Arial"/>
@@ -415,171 +406,149 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+  <cellXfs count="60">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -590,24 +559,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -623,20 +653,32 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4" name="Agrupar"/>
+        <xdr:cNvPr id="4" name="Agrupar">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="56554" y="38436"/>
-          <a:ext cx="1035647" cy="700062"/>
+          <a:ext cx="1030566" cy="689902"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="1035646" cy="700060"/>
         </a:xfrm>
       </xdr:grpSpPr>
-      <xdr:sp>
+      <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="2" name="Rectángulo"/>
+          <xdr:cNvPr id="2" name="Rectángulo">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvSpPr/>
         </xdr:nvSpPr>
         <xdr:spPr>
@@ -660,21 +702,25 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr/>
+            <a:endParaRPr/>
           </a:p>
         </xdr:txBody>
       </xdr:sp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="3" name="image.png" descr="image.png"/>
+          <xdr:cNvPr id="3" name="image.png" descr="image.png">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1"/>
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip r:embed="rId1">
-            <a:extLst/>
-          </a:blip>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -701,7 +747,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Tema de Office">
       <a:dk1>
@@ -903,7 +949,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -921,7 +967,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -950,7 +996,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -975,7 +1021,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1000,7 +1046,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1025,7 +1071,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1050,7 +1096,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1075,7 +1121,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1100,7 +1146,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1125,7 +1171,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1150,7 +1196,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1163,9 +1209,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1182,7 +1234,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1200,7 +1252,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1225,7 +1277,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1250,7 +1302,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1275,7 +1327,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1300,7 +1352,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1325,7 +1377,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1350,7 +1402,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1375,7 +1427,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1400,7 +1452,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1425,7 +1477,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1438,9 +1490,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1454,7 +1512,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1472,7 +1530,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1501,7 +1559,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1526,7 +1584,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1551,7 +1609,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1576,7 +1634,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1601,7 +1659,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1626,7 +1684,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1651,7 +1709,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1676,7 +1734,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1701,7 +1759,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1714,577 +1772,585 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AR27"/>
-  <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="14.65" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.796875" defaultRowHeight="14.7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="3.35156" style="1" customWidth="1"/>
-    <col min="4" max="4" width="2.67188" style="1" customWidth="1"/>
-    <col min="5" max="35" width="3.35156" style="1" customWidth="1"/>
+    <col min="1" max="3" width="3.296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="2.69921875" style="1" customWidth="1"/>
+    <col min="5" max="35" width="3.296875" style="1" customWidth="1"/>
     <col min="36" max="36" width="4" style="1" customWidth="1"/>
-    <col min="37" max="38" width="4.35156" style="1" customWidth="1"/>
+    <col min="37" max="38" width="4.296875" style="1" customWidth="1"/>
     <col min="39" max="39" width="4" style="1" customWidth="1"/>
-    <col min="40" max="40" width="4.35156" style="1" customWidth="1"/>
-    <col min="41" max="44" width="3.35156" style="1" customWidth="1"/>
-    <col min="45" max="16384" width="10.8516" style="1" customWidth="1"/>
+    <col min="40" max="40" width="4.296875" style="1" customWidth="1"/>
+    <col min="41" max="44" width="3.296875" style="1" customWidth="1"/>
+    <col min="45" max="45" width="10.796875" style="1" customWidth="1"/>
+    <col min="46" max="16384" width="10.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" t="s" s="4">
+    <row r="1" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="33"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
-      <c r="R1" s="5"/>
-      <c r="S1" s="5"/>
-      <c r="T1" s="5"/>
-      <c r="U1" s="5"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
-      <c r="X1" s="5"/>
-      <c r="Y1" s="5"/>
-      <c r="Z1" s="5"/>
-      <c r="AA1" s="5"/>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="5"/>
-      <c r="AF1" s="5"/>
-      <c r="AG1" s="5"/>
-      <c r="AH1" s="5"/>
-      <c r="AI1" s="5"/>
-      <c r="AJ1" s="5"/>
-      <c r="AK1" s="5"/>
-      <c r="AL1" s="5"/>
-      <c r="AM1" s="5"/>
-      <c r="AN1" s="6"/>
-      <c r="AO1" s="7"/>
-      <c r="AP1" s="8"/>
-      <c r="AQ1" s="8"/>
-      <c r="AR1" s="8"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="55"/>
+      <c r="U1" s="55"/>
+      <c r="V1" s="55"/>
+      <c r="W1" s="55"/>
+      <c r="X1" s="55"/>
+      <c r="Y1" s="55"/>
+      <c r="Z1" s="55"/>
+      <c r="AA1" s="55"/>
+      <c r="AB1" s="55"/>
+      <c r="AC1" s="55"/>
+      <c r="AD1" s="55"/>
+      <c r="AE1" s="55"/>
+      <c r="AF1" s="55"/>
+      <c r="AG1" s="55"/>
+      <c r="AH1" s="55"/>
+      <c r="AI1" s="55"/>
+      <c r="AJ1" s="55"/>
+      <c r="AK1" s="55"/>
+      <c r="AL1" s="55"/>
+      <c r="AM1" s="55"/>
+      <c r="AN1" s="3"/>
+      <c r="AO1" s="4"/>
+      <c r="AP1" s="5"/>
+      <c r="AQ1" s="5"/>
+      <c r="AR1" s="5"/>
     </row>
-    <row r="2" ht="8" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
-      <c r="X2" s="10"/>
-      <c r="Y2" s="10"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="9"/>
-      <c r="AN2" s="11"/>
-      <c r="AO2" s="12"/>
-      <c r="AP2" s="8"/>
-      <c r="AQ2" s="8"/>
-      <c r="AR2" s="8"/>
+    <row r="2" spans="1:44" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6"/>
+      <c r="AN2" s="8"/>
+      <c r="AO2" s="9"/>
+      <c r="AP2" s="5"/>
+      <c r="AQ2" s="5"/>
+      <c r="AR2" s="5"/>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" t="s" s="14">
+    <row r="3" spans="1:44" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="33"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="N3" s="33"/>
+      <c r="O3" s="33"/>
+      <c r="P3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="12"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="15"/>
-      <c r="AK3" t="s" s="16">
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="33"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="33"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="5"/>
+      <c r="AB3" s="5"/>
+      <c r="AC3" s="5"/>
+      <c r="AD3" s="5"/>
+      <c r="AE3" s="5"/>
+      <c r="AF3" s="5"/>
+      <c r="AG3" s="5"/>
+      <c r="AH3" s="5"/>
+      <c r="AI3" s="5"/>
+      <c r="AJ3" s="12"/>
+      <c r="AK3" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="AL3" s="17"/>
-      <c r="AM3" s="17"/>
-      <c r="AN3" s="18"/>
-      <c r="AO3" s="12"/>
-      <c r="AP3" s="8"/>
-      <c r="AQ3" s="8"/>
-      <c r="AR3" s="8"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="13"/>
+      <c r="AO3" s="9"/>
+      <c r="AP3" s="5"/>
+      <c r="AQ3" s="5"/>
+      <c r="AR3" s="5"/>
     </row>
-    <row r="4" ht="14.65" customHeight="1">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="20"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-      <c r="V4" s="19"/>
-      <c r="W4" s="19"/>
-      <c r="X4" s="19"/>
-      <c r="Y4" s="20"/>
-      <c r="Z4" s="13"/>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="8"/>
-      <c r="AF4" s="8"/>
-      <c r="AG4" s="13"/>
-      <c r="AH4" s="13"/>
-      <c r="AI4" s="21"/>
-      <c r="AJ4" s="15"/>
-      <c r="AK4" s="22"/>
-      <c r="AL4" s="22"/>
-      <c r="AM4" s="22"/>
-      <c r="AN4" s="18"/>
-      <c r="AO4" s="12"/>
-      <c r="AP4" s="8"/>
-      <c r="AQ4" s="8"/>
-      <c r="AR4" s="8"/>
+    <row r="4" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="14"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="14"/>
+      <c r="W4" s="14"/>
+      <c r="X4" s="14"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="16"/>
+      <c r="AJ4" s="12"/>
+      <c r="AK4" s="58"/>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="58"/>
+      <c r="AN4" s="13"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="5"/>
+      <c r="AQ4" s="5"/>
+      <c r="AR4" s="5"/>
     </row>
-    <row r="5" ht="14.65" customHeight="1">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="8"/>
-      <c r="E5" t="s" s="24">
+    <row r="5" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="52"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="12"/>
-      <c r="P5" t="s" s="24">
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="Q5" s="25"/>
+      <c r="Q5" s="47"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="25"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="17"/>
+      <c r="X5" s="18"/>
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" t="s" s="24">
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="AC5" s="25"/>
-      <c r="AD5" s="25"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="25"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="26"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="33"/>
+      <c r="AH5" s="33"/>
+      <c r="AI5" s="33"/>
+      <c r="AJ5" s="19"/>
       <c r="AK5" s="2"/>
       <c r="AL5" s="2"/>
       <c r="AM5" s="2"/>
-      <c r="AN5" s="26"/>
-      <c r="AO5" s="12"/>
-      <c r="AP5" s="8"/>
-      <c r="AQ5" s="8"/>
-      <c r="AR5" s="8"/>
+      <c r="AN5" s="19"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="5"/>
+      <c r="AQ5" s="5"/>
+      <c r="AR5" s="5"/>
     </row>
-    <row r="6" ht="14.65" customHeight="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-      <c r="AE6" s="28"/>
-      <c r="AF6" s="28"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="29"/>
-      <c r="AJ6" s="11"/>
+    <row r="6" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="21"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="21"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="5"/>
+      <c r="AB6" s="21"/>
+      <c r="AC6" s="21"/>
+      <c r="AD6" s="21"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="21"/>
+      <c r="AG6" s="22"/>
+      <c r="AH6" s="22"/>
+      <c r="AI6" s="22"/>
+      <c r="AJ6" s="8"/>
       <c r="AK6" s="2"/>
       <c r="AL6" s="2"/>
       <c r="AM6" s="2"/>
-      <c r="AN6" s="26"/>
-      <c r="AO6" s="12"/>
-      <c r="AP6" s="8"/>
-      <c r="AQ6" s="8"/>
-      <c r="AR6" s="8"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="5"/>
+      <c r="AQ6" s="5"/>
+      <c r="AR6" s="5"/>
     </row>
-    <row r="7" ht="8" customHeight="1">
-      <c r="A7" s="30"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="20"/>
-      <c r="AL7" s="20"/>
-      <c r="AM7" s="20"/>
-      <c r="AN7" s="31"/>
-      <c r="AO7" s="12"/>
-      <c r="AP7" s="8"/>
-      <c r="AQ7" s="8"/>
-      <c r="AR7" s="8"/>
+    <row r="7" spans="1:44" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
+      <c r="AA7" s="10"/>
+      <c r="AB7" s="10"/>
+      <c r="AC7" s="10"/>
+      <c r="AD7" s="10"/>
+      <c r="AE7" s="10"/>
+      <c r="AF7" s="10"/>
+      <c r="AG7" s="10"/>
+      <c r="AH7" s="10"/>
+      <c r="AI7" s="10"/>
+      <c r="AJ7" s="10"/>
+      <c r="AK7" s="15"/>
+      <c r="AL7" s="15"/>
+      <c r="AM7" s="15"/>
+      <c r="AN7" s="24"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="5"/>
+      <c r="AQ7" s="5"/>
+      <c r="AR7" s="5"/>
     </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" t="s" s="32">
+    <row r="8" spans="1:44" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" t="s" s="34">
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" t="s" s="34">
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="35"/>
-      <c r="W8" s="35"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="35"/>
-      <c r="Z8" s="35"/>
-      <c r="AA8" t="s" s="34">
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="43"/>
+      <c r="V8" s="43"/>
+      <c r="W8" s="43"/>
+      <c r="X8" s="43"/>
+      <c r="Y8" s="43"/>
+      <c r="Z8" s="43"/>
+      <c r="AA8" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="AB8" s="35"/>
-      <c r="AC8" s="35"/>
-      <c r="AD8" s="35"/>
-      <c r="AE8" s="35"/>
-      <c r="AF8" s="35"/>
-      <c r="AG8" s="35"/>
-      <c r="AH8" t="s" s="34">
+      <c r="AB8" s="43"/>
+      <c r="AC8" s="43"/>
+      <c r="AD8" s="43"/>
+      <c r="AE8" s="43"/>
+      <c r="AF8" s="43"/>
+      <c r="AG8" s="43"/>
+      <c r="AH8" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="AI8" s="35"/>
-      <c r="AJ8" s="35"/>
-      <c r="AK8" t="s" s="36">
+      <c r="AI8" s="43"/>
+      <c r="AJ8" s="43"/>
+      <c r="AK8" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="AL8" s="37"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="12"/>
-      <c r="AP8" s="8"/>
-      <c r="AQ8" s="8"/>
-      <c r="AR8" s="8"/>
+      <c r="AL8" s="41"/>
+      <c r="AM8" s="41"/>
+      <c r="AN8" s="41"/>
+      <c r="AO8" s="9"/>
+      <c r="AP8" s="5"/>
+      <c r="AQ8" s="5"/>
+      <c r="AR8" s="5"/>
     </row>
-    <row r="9" ht="14.65" customHeight="1">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="35"/>
-      <c r="M9" t="s" s="34">
+    <row r="9" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="50"/>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" t="s" s="34">
+      <c r="N9" s="43"/>
+      <c r="O9" s="43"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="35"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="35"/>
-      <c r="AE9" s="35"/>
-      <c r="AF9" s="35"/>
-      <c r="AG9" s="35"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="35"/>
-      <c r="AJ9" s="35"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="37"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="12"/>
-      <c r="AP9" s="8"/>
-      <c r="AQ9" s="8"/>
-      <c r="AR9" s="8"/>
+      <c r="U9" s="43"/>
+      <c r="V9" s="43"/>
+      <c r="W9" s="43"/>
+      <c r="X9" s="43"/>
+      <c r="Y9" s="43"/>
+      <c r="Z9" s="43"/>
+      <c r="AA9" s="43"/>
+      <c r="AB9" s="43"/>
+      <c r="AC9" s="43"/>
+      <c r="AD9" s="43"/>
+      <c r="AE9" s="43"/>
+      <c r="AF9" s="43"/>
+      <c r="AG9" s="43"/>
+      <c r="AH9" s="43"/>
+      <c r="AI9" s="43"/>
+      <c r="AJ9" s="43"/>
+      <c r="AK9" s="41"/>
+      <c r="AL9" s="41"/>
+      <c r="AM9" s="41"/>
+      <c r="AN9" s="41"/>
+      <c r="AO9" s="9"/>
+      <c r="AP9" s="5"/>
+      <c r="AQ9" s="5"/>
+      <c r="AR9" s="5"/>
     </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" t="s" s="41">
+    <row r="10" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="E10" t="s" s="42">
+      <c r="E10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44">
+      <c r="F10" s="45"/>
+      <c r="G10" s="30">
         <v>0</v>
       </c>
-      <c r="H10" s="45">
+      <c r="H10" s="31">
         <v>1</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="31">
         <v>2</v>
       </c>
-      <c r="J10" s="45">
+      <c r="J10" s="31">
         <v>3</v>
       </c>
-      <c r="K10" t="s" s="34">
+      <c r="K10" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="35"/>
-      <c r="M10" t="s" s="42">
+      <c r="L10" s="43"/>
+      <c r="M10" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="N10" s="43"/>
-      <c r="O10" s="45">
+      <c r="N10" s="45"/>
+      <c r="O10" s="31">
         <v>0</v>
       </c>
-      <c r="P10" s="45">
+      <c r="P10" s="31">
         <v>1</v>
       </c>
-      <c r="Q10" s="45">
+      <c r="Q10" s="31">
         <v>2</v>
       </c>
-      <c r="R10" s="45">
+      <c r="R10" s="31">
         <v>3</v>
       </c>
-      <c r="S10" s="45">
+      <c r="S10" s="31">
         <v>4</v>
       </c>
-      <c r="T10" t="s" s="42">
+      <c r="T10" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="U10" s="43"/>
-      <c r="V10" s="45">
+      <c r="U10" s="45"/>
+      <c r="V10" s="31">
         <v>0</v>
       </c>
-      <c r="W10" s="45">
+      <c r="W10" s="31">
         <v>1</v>
       </c>
-      <c r="X10" s="45">
+      <c r="X10" s="31">
         <v>2</v>
       </c>
-      <c r="Y10" s="45">
+      <c r="Y10" s="31">
         <v>3</v>
       </c>
-      <c r="Z10" s="45">
+      <c r="Z10" s="31">
         <v>4</v>
       </c>
-      <c r="AA10" s="45">
+      <c r="AA10" s="31">
         <v>0</v>
       </c>
-      <c r="AB10" s="45">
+      <c r="AB10" s="31">
         <v>1</v>
       </c>
-      <c r="AC10" s="45">
+      <c r="AC10" s="31">
         <v>2</v>
       </c>
-      <c r="AD10" s="45">
+      <c r="AD10" s="31">
         <v>3</v>
       </c>
-      <c r="AE10" s="45">
+      <c r="AE10" s="31">
         <v>4</v>
       </c>
-      <c r="AF10" t="s" s="34">
+      <c r="AF10" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AG10" s="35"/>
-      <c r="AH10" t="s" s="34">
+      <c r="AG10" s="43"/>
+      <c r="AH10" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="AI10" t="s" s="34">
+      <c r="AI10" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AJ10" t="s" s="34">
+      <c r="AJ10" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="37"/>
-      <c r="AM10" s="37"/>
-      <c r="AN10" s="37"/>
-      <c r="AO10" s="12"/>
-      <c r="AP10" s="8"/>
-      <c r="AQ10" s="8"/>
-      <c r="AR10" s="8"/>
+      <c r="AK10" s="41"/>
+      <c r="AL10" s="41"/>
+      <c r="AM10" s="41"/>
+      <c r="AN10" s="41"/>
+      <c r="AO10" s="9"/>
+      <c r="AP10" s="5"/>
+      <c r="AQ10" s="5"/>
+      <c r="AR10" s="5"/>
     </row>
-    <row r="11" ht="20.1" customHeight="1">
+    <row r="11" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2321,16 +2387,16 @@
       <c r="AH11" s="2"/>
       <c r="AI11" s="2"/>
       <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
-      <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="12"/>
-      <c r="AP11" s="8"/>
-      <c r="AQ11" s="8"/>
-      <c r="AR11" s="8"/>
+      <c r="AK11" s="33"/>
+      <c r="AL11" s="33"/>
+      <c r="AM11" s="33"/>
+      <c r="AN11" s="33"/>
+      <c r="AO11" s="9"/>
+      <c r="AP11" s="5"/>
+      <c r="AQ11" s="5"/>
+      <c r="AR11" s="5"/>
     </row>
-    <row r="12" ht="20.1" customHeight="1">
+    <row r="12" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2367,16 +2433,16 @@
       <c r="AH12" s="2"/>
       <c r="AI12" s="2"/>
       <c r="AJ12" s="2"/>
-      <c r="AK12" s="2"/>
-      <c r="AL12" s="2"/>
-      <c r="AM12" s="2"/>
-      <c r="AN12" s="2"/>
-      <c r="AO12" s="12"/>
-      <c r="AP12" s="8"/>
-      <c r="AQ12" s="8"/>
-      <c r="AR12" s="8"/>
+      <c r="AK12" s="33"/>
+      <c r="AL12" s="33"/>
+      <c r="AM12" s="33"/>
+      <c r="AN12" s="33"/>
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="5"/>
+      <c r="AQ12" s="5"/>
+      <c r="AR12" s="5"/>
     </row>
-    <row r="13" ht="20.1" customHeight="1">
+    <row r="13" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2413,20 +2479,20 @@
       <c r="AH13" s="2"/>
       <c r="AI13" s="2"/>
       <c r="AJ13" s="2"/>
-      <c r="AK13" s="2"/>
-      <c r="AL13" s="2"/>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="12"/>
-      <c r="AP13" s="8"/>
-      <c r="AQ13" s="8"/>
-      <c r="AR13" s="8"/>
+      <c r="AK13" s="33"/>
+      <c r="AL13" s="33"/>
+      <c r="AM13" s="33"/>
+      <c r="AN13" s="33"/>
+      <c r="AO13" s="9"/>
+      <c r="AP13" s="5"/>
+      <c r="AQ13" s="5"/>
+      <c r="AR13" s="5"/>
     </row>
-    <row r="14" ht="20.1" customHeight="1">
+    <row r="14" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="46"/>
+      <c r="D14" s="32"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -2459,22 +2525,22 @@
       <c r="AH14" s="2"/>
       <c r="AI14" s="2"/>
       <c r="AJ14" s="2"/>
-      <c r="AK14" t="s" s="36">
+      <c r="AK14" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="AL14" s="37"/>
-      <c r="AM14" s="37"/>
-      <c r="AN14" s="37"/>
-      <c r="AO14" s="12"/>
-      <c r="AP14" s="8"/>
-      <c r="AQ14" s="8"/>
-      <c r="AR14" s="8"/>
+      <c r="AL14" s="41"/>
+      <c r="AM14" s="41"/>
+      <c r="AN14" s="41"/>
+      <c r="AO14" s="9"/>
+      <c r="AP14" s="5"/>
+      <c r="AQ14" s="5"/>
+      <c r="AR14" s="5"/>
     </row>
-    <row r="15" ht="20.1" customHeight="1">
+    <row r="15" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="46"/>
+      <c r="D15" s="32"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -2507,22 +2573,22 @@
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
       <c r="AJ15" s="2"/>
-      <c r="AK15" t="s" s="36">
+      <c r="AK15" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="AL15" s="2"/>
-      <c r="AM15" s="2"/>
-      <c r="AN15" s="2"/>
-      <c r="AO15" s="12"/>
-      <c r="AP15" s="8"/>
-      <c r="AQ15" s="8"/>
-      <c r="AR15" s="8"/>
+      <c r="AL15" s="33"/>
+      <c r="AM15" s="33"/>
+      <c r="AN15" s="33"/>
+      <c r="AO15" s="9"/>
+      <c r="AP15" s="5"/>
+      <c r="AQ15" s="5"/>
+      <c r="AR15" s="5"/>
     </row>
-    <row r="16" ht="20.1" customHeight="1">
+    <row r="16" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="46"/>
+      <c r="D16" s="32"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -2555,22 +2621,22 @@
       <c r="AH16" s="2"/>
       <c r="AI16" s="2"/>
       <c r="AJ16" s="2"/>
-      <c r="AK16" t="s" s="36">
+      <c r="AK16" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="AL16" s="2"/>
-      <c r="AM16" s="2"/>
-      <c r="AN16" s="2"/>
-      <c r="AO16" s="12"/>
-      <c r="AP16" s="8"/>
-      <c r="AQ16" s="8"/>
-      <c r="AR16" s="8"/>
+      <c r="AL16" s="33"/>
+      <c r="AM16" s="33"/>
+      <c r="AN16" s="33"/>
+      <c r="AO16" s="9"/>
+      <c r="AP16" s="5"/>
+      <c r="AQ16" s="5"/>
+      <c r="AR16" s="5"/>
     </row>
-    <row r="17" ht="20.1" customHeight="1">
+    <row r="17" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="46"/>
+      <c r="D17" s="32"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -2603,22 +2669,22 @@
       <c r="AH17" s="2"/>
       <c r="AI17" s="2"/>
       <c r="AJ17" s="2"/>
-      <c r="AK17" t="s" s="36">
+      <c r="AK17" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="AL17" s="2"/>
-      <c r="AM17" s="2"/>
-      <c r="AN17" s="2"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="8"/>
-      <c r="AQ17" s="8"/>
-      <c r="AR17" s="8"/>
+      <c r="AL17" s="33"/>
+      <c r="AM17" s="33"/>
+      <c r="AN17" s="33"/>
+      <c r="AO17" s="9"/>
+      <c r="AP17" s="5"/>
+      <c r="AQ17" s="5"/>
+      <c r="AR17" s="5"/>
     </row>
-    <row r="18" ht="20.1" customHeight="1">
+    <row r="18" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="46"/>
+      <c r="D18" s="32"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -2651,22 +2717,22 @@
       <c r="AH18" s="2"/>
       <c r="AI18" s="2"/>
       <c r="AJ18" s="2"/>
-      <c r="AK18" t="s" s="36">
+      <c r="AK18" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="AL18" s="2"/>
-      <c r="AM18" s="2"/>
-      <c r="AN18" s="2"/>
-      <c r="AO18" s="12"/>
-      <c r="AP18" s="8"/>
-      <c r="AQ18" s="8"/>
-      <c r="AR18" s="8"/>
+      <c r="AL18" s="33"/>
+      <c r="AM18" s="33"/>
+      <c r="AN18" s="33"/>
+      <c r="AO18" s="9"/>
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5"/>
+      <c r="AR18" s="5"/>
     </row>
-    <row r="19" ht="20.1" customHeight="1">
+    <row r="19" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="46"/>
+      <c r="D19" s="32"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -2699,22 +2765,22 @@
       <c r="AH19" s="2"/>
       <c r="AI19" s="2"/>
       <c r="AJ19" s="2"/>
-      <c r="AK19" t="s" s="36">
+      <c r="AK19" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="2"/>
-      <c r="AO19" s="12"/>
-      <c r="AP19" s="8"/>
-      <c r="AQ19" s="8"/>
-      <c r="AR19" s="8"/>
+      <c r="AL19" s="33"/>
+      <c r="AM19" s="33"/>
+      <c r="AN19" s="33"/>
+      <c r="AO19" s="9"/>
+      <c r="AP19" s="5"/>
+      <c r="AQ19" s="5"/>
+      <c r="AR19" s="5"/>
     </row>
-    <row r="20" ht="20.1" customHeight="1">
+    <row r="20" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="46"/>
+      <c r="D20" s="32"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -2747,22 +2813,22 @@
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
       <c r="AJ20" s="2"/>
-      <c r="AK20" t="s" s="36">
+      <c r="AK20" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="AL20" s="2"/>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2"/>
-      <c r="AO20" s="12"/>
-      <c r="AP20" s="8"/>
-      <c r="AQ20" s="8"/>
-      <c r="AR20" s="8"/>
+      <c r="AL20" s="33"/>
+      <c r="AM20" s="33"/>
+      <c r="AN20" s="33"/>
+      <c r="AO20" s="9"/>
+      <c r="AP20" s="5"/>
+      <c r="AQ20" s="5"/>
+      <c r="AR20" s="5"/>
     </row>
-    <row r="21" ht="20.1" customHeight="1">
+    <row r="21" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="46"/>
+      <c r="D21" s="32"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -2795,20 +2861,20 @@
       <c r="AH21" s="2"/>
       <c r="AI21" s="2"/>
       <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
-      <c r="AL21" s="2"/>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2"/>
-      <c r="AO21" s="12"/>
-      <c r="AP21" s="8"/>
-      <c r="AQ21" s="8"/>
-      <c r="AR21" s="8"/>
+      <c r="AK21" s="33"/>
+      <c r="AL21" s="33"/>
+      <c r="AM21" s="33"/>
+      <c r="AN21" s="33"/>
+      <c r="AO21" s="9"/>
+      <c r="AP21" s="5"/>
+      <c r="AQ21" s="5"/>
+      <c r="AR21" s="5"/>
     </row>
-    <row r="22" ht="20.1" customHeight="1">
+    <row r="22" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="46"/>
+      <c r="D22" s="32"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -2841,20 +2907,20 @@
       <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2"/>
-      <c r="AK22" s="2"/>
-      <c r="AL22" s="2"/>
-      <c r="AM22" s="2"/>
-      <c r="AN22" s="2"/>
-      <c r="AO22" s="12"/>
-      <c r="AP22" s="8"/>
-      <c r="AQ22" s="8"/>
-      <c r="AR22" s="8"/>
+      <c r="AK22" s="33"/>
+      <c r="AL22" s="33"/>
+      <c r="AM22" s="33"/>
+      <c r="AN22" s="33"/>
+      <c r="AO22" s="9"/>
+      <c r="AP22" s="5"/>
+      <c r="AQ22" s="5"/>
+      <c r="AR22" s="5"/>
     </row>
-    <row r="23" ht="20.1" customHeight="1">
+    <row r="23" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="46"/>
+      <c r="D23" s="32"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -2887,20 +2953,20 @@
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
       <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
-      <c r="AL23" s="2"/>
-      <c r="AM23" s="2"/>
-      <c r="AN23" s="2"/>
-      <c r="AO23" s="12"/>
-      <c r="AP23" s="8"/>
-      <c r="AQ23" s="8"/>
-      <c r="AR23" s="8"/>
+      <c r="AK23" s="33"/>
+      <c r="AL23" s="33"/>
+      <c r="AM23" s="33"/>
+      <c r="AN23" s="33"/>
+      <c r="AO23" s="9"/>
+      <c r="AP23" s="5"/>
+      <c r="AQ23" s="5"/>
+      <c r="AR23" s="5"/>
     </row>
-    <row r="24" ht="20.1" customHeight="1">
+    <row r="24" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="46"/>
+      <c r="D24" s="32"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -2933,22 +2999,22 @@
       <c r="AH24" s="2"/>
       <c r="AI24" s="2"/>
       <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
-      <c r="AO24" s="12"/>
-      <c r="AP24" s="8"/>
-      <c r="AQ24" s="8"/>
-      <c r="AR24" s="8"/>
+      <c r="AK24" s="33"/>
+      <c r="AL24" s="33"/>
+      <c r="AM24" s="33"/>
+      <c r="AN24" s="33"/>
+      <c r="AO24" s="9"/>
+      <c r="AP24" s="5"/>
+      <c r="AQ24" s="5"/>
+      <c r="AR24" s="5"/>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" t="s" s="47">
+    <row r="25" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="46"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="32"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -2981,20 +3047,20 @@
       <c r="AH25" s="2"/>
       <c r="AI25" s="2"/>
       <c r="AJ25" s="2"/>
-      <c r="AK25" s="2"/>
-      <c r="AL25" s="2"/>
-      <c r="AM25" s="2"/>
-      <c r="AN25" s="2"/>
-      <c r="AO25" s="12"/>
-      <c r="AP25" s="8"/>
-      <c r="AQ25" s="8"/>
-      <c r="AR25" s="8"/>
+      <c r="AK25" s="33"/>
+      <c r="AL25" s="33"/>
+      <c r="AM25" s="33"/>
+      <c r="AN25" s="33"/>
+      <c r="AO25" s="9"/>
+      <c r="AP25" s="5"/>
+      <c r="AQ25" s="5"/>
+      <c r="AR25" s="5"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="46"/>
+    <row r="26" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="35"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="32"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -3027,107 +3093,65 @@
       <c r="AH26" s="2"/>
       <c r="AI26" s="2"/>
       <c r="AJ26" s="2"/>
-      <c r="AK26" s="2"/>
-      <c r="AL26" s="2"/>
-      <c r="AM26" s="2"/>
-      <c r="AN26" s="2"/>
-      <c r="AO26" s="12"/>
-      <c r="AP26" s="8"/>
-      <c r="AQ26" s="8"/>
-      <c r="AR26" s="8"/>
+      <c r="AK26" s="33"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="33"/>
+      <c r="AN26" s="33"/>
+      <c r="AO26" s="9"/>
+      <c r="AP26" s="5"/>
+      <c r="AQ26" s="5"/>
+      <c r="AR26" s="5"/>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" t="s" s="49">
+    <row r="27" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="51"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="53"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="52"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="2"/>
-      <c r="V27" s="2"/>
-      <c r="W27" s="2"/>
-      <c r="X27" s="2"/>
-      <c r="Y27" s="2"/>
-      <c r="Z27" s="2"/>
-      <c r="AA27" s="2"/>
-      <c r="AB27" s="2"/>
-      <c r="AC27" s="2"/>
-      <c r="AD27" s="2"/>
-      <c r="AE27" s="2"/>
-      <c r="AF27" s="2"/>
-      <c r="AG27" s="2"/>
-      <c r="AH27" s="2"/>
-      <c r="AI27" s="2"/>
-      <c r="AJ27" s="2"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="59"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="51"/>
+      <c r="R27" s="39"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="33"/>
+      <c r="AE27" s="33"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="33"/>
+      <c r="AH27" s="33"/>
+      <c r="AI27" s="33"/>
+      <c r="AJ27" s="33"/>
       <c r="AK27" s="2"/>
       <c r="AL27" s="2"/>
       <c r="AM27" s="2"/>
       <c r="AN27" s="2"/>
-      <c r="AO27" s="12"/>
-      <c r="AP27" s="8"/>
-      <c r="AQ27" s="8"/>
-      <c r="AR27" s="8"/>
+      <c r="AO27" s="9"/>
+      <c r="AP27" s="5"/>
+      <c r="AQ27" s="5"/>
+      <c r="AR27" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="61">
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="AK24:AN24"/>
-    <mergeCell ref="A25:C26"/>
-    <mergeCell ref="AK25:AN25"/>
-    <mergeCell ref="AK26:AN26"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:L27"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="AL20:AN20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="AK21:AN21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="AK22:AN23"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="AL17:AN17"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="AL18:AN18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="AL19:AN19"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="AK14:AN14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="AK11:AN11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AM12:AN12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="AK13:AL13"/>
-    <mergeCell ref="AM13:AN13"/>
-    <mergeCell ref="AK8:AN10"/>
-    <mergeCell ref="M9:S9"/>
-    <mergeCell ref="T9:Z9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="AF10:AG10"/>
+  <mergeCells count="47">
     <mergeCell ref="AB5:AF5"/>
     <mergeCell ref="AG5:AI5"/>
     <mergeCell ref="A8:D9"/>
@@ -3143,13 +3167,41 @@
     <mergeCell ref="E5:H5"/>
     <mergeCell ref="P5:Q5"/>
     <mergeCell ref="I5:N5"/>
+    <mergeCell ref="AK13:AL13"/>
+    <mergeCell ref="AM13:AN13"/>
+    <mergeCell ref="AK8:AN10"/>
+    <mergeCell ref="M9:S9"/>
+    <mergeCell ref="T9:Z9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="T10:U10"/>
+    <mergeCell ref="AF10:AG10"/>
+    <mergeCell ref="AK11:AN11"/>
+    <mergeCell ref="AK12:AL12"/>
+    <mergeCell ref="AM12:AN12"/>
+    <mergeCell ref="AK14:AN14"/>
+    <mergeCell ref="AL15:AN15"/>
+    <mergeCell ref="AL16:AN16"/>
+    <mergeCell ref="AL17:AN17"/>
+    <mergeCell ref="AL18:AN18"/>
+    <mergeCell ref="AL19:AN19"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:L27"/>
+    <mergeCell ref="AL20:AN20"/>
+    <mergeCell ref="AK21:AN21"/>
+    <mergeCell ref="AK22:AN23"/>
     <mergeCell ref="M27:S27"/>
     <mergeCell ref="T27:Z27"/>
     <mergeCell ref="AA27:AG27"/>
     <mergeCell ref="AH27:AJ27"/>
+    <mergeCell ref="AK24:AN24"/>
+    <mergeCell ref="A25:C26"/>
+    <mergeCell ref="AK25:AN25"/>
+    <mergeCell ref="AK26:AN26"/>
   </mergeCells>
-  <pageMargins left="0.35" right="0.196457" top="0.91063" bottom="0.965354" header="0.429921" footer="0.670079"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="landscape" pageOrder="overThenDown"/>
+  <pageMargins left="0.35" right="0.19645699999999999" top="0.91063000000000005" bottom="0.96535400000000005" header="0.429921" footer="0.67007899999999998"/>
+  <pageSetup pageOrder="overThenDown" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Arial,Regular"&amp;14&amp;K000000CURSO NACIONAL DE ENTRENADORES NIVEL I</oddHeader>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>

--- a/proyFinal/src/datos/plantilla_de_estadisticas.xlsx
+++ b/proyFinal/src/datos/plantilla_de_estadisticas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizas\proyectoFinal\proyFinal\src\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABF614A-933D-47C2-B36D-F8C7F00AE307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37030658-F1C8-4286-80F4-ABD091347062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-1728" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -20,18 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>ESTADISTICA INDIVIDUAL DE JUEGO</t>
   </si>
   <si>
     <t>vs</t>
-  </si>
-  <si>
-    <t>FORMACION INICIAL</t>
-  </si>
-  <si>
-    <t>TORNEO</t>
   </si>
   <si>
     <t>FECHA</t>
@@ -53,9 +47,6 @@
   </si>
   <si>
     <t>BLOQUEO</t>
-  </si>
-  <si>
-    <t>GESTION-.ERRORES</t>
   </si>
   <si>
     <t>ROTACION</t>
@@ -88,35 +79,17 @@
     <t>TOT</t>
   </si>
   <si>
-    <t>SUSTITUCIONES</t>
+    <t xml:space="preserve"> OBSERVACIONES</t>
   </si>
   <si>
-    <t>1º</t>
-  </si>
-  <si>
-    <t>2º</t>
-  </si>
-  <si>
-    <t>3º</t>
-  </si>
-  <si>
-    <t>4º</t>
-  </si>
-  <si>
-    <t>5º</t>
-  </si>
-  <si>
-    <t>6º</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> OBSERVACIONES</t>
+    <t>PARTIDO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -136,12 +109,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
@@ -171,7 +138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -229,10 +196,10 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
@@ -241,16 +208,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -259,7 +226,7 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
         <color indexed="10"/>
@@ -271,7 +238,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
         <color indexed="10"/>
@@ -280,13 +247,13 @@
         <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
@@ -301,16 +268,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -319,13 +286,13 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -334,10 +301,10 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -346,7 +313,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
@@ -355,7 +322,7 @@
         <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -363,11 +330,33 @@
       <left style="thin">
         <color indexed="8"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -376,99 +365,199 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -480,27 +569,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -509,47 +590,77 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -634,116 +745,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>56554</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>38436</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>179698</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="4" name="Agrupar">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="56554" y="38436"/>
-          <a:ext cx="1030566" cy="689902"/>
-          <a:chOff x="0" y="0"/>
-          <a:chExt cx="1035646" cy="700060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="2" name="Rectángulo">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="0" y="-1"/>
-            <a:ext cx="1035647" cy="700062"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="000080"/>
-          </a:solidFill>
-          <a:ln w="12700" cap="flat">
-            <a:noFill/>
-            <a:miter lim="400000"/>
-          </a:ln>
-          <a:effectLst/>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="3" name="image.png" descr="image.png">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="0" y="-1"/>
-            <a:ext cx="1035647" cy="700062"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln w="12700" cap="flat">
-            <a:noFill/>
-            <a:miter lim="400000"/>
-          </a:ln>
-          <a:effectLst/>
-        </xdr:spPr>
-      </xdr:pic>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1791,566 +1792,458 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.796875" defaultRowHeight="14.7" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AH27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.75" defaultRowHeight="14.65" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="3.296875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="2.69921875" style="1" customWidth="1"/>
-    <col min="5" max="35" width="3.296875" style="1" customWidth="1"/>
-    <col min="36" max="36" width="4" style="1" customWidth="1"/>
-    <col min="37" max="38" width="4.296875" style="1" customWidth="1"/>
-    <col min="39" max="39" width="4" style="1" customWidth="1"/>
-    <col min="40" max="40" width="4.296875" style="1" customWidth="1"/>
-    <col min="41" max="44" width="3.296875" style="1" customWidth="1"/>
-    <col min="45" max="45" width="10.796875" style="1" customWidth="1"/>
-    <col min="46" max="16384" width="10.796875" style="1"/>
+    <col min="1" max="1" width="9.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.875" style="1" customWidth="1"/>
+    <col min="3" max="33" width="3.25" style="1" customWidth="1"/>
+    <col min="34" max="34" width="4" style="1" customWidth="1"/>
+    <col min="35" max="35" width="10.75" style="1" customWidth="1"/>
+    <col min="36" max="16384" width="10.75" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
-      <c r="B1" s="33"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="54" t="s">
+    <row r="1" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="55"/>
-      <c r="P1" s="55"/>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="55"/>
-      <c r="Y1" s="55"/>
-      <c r="Z1" s="55"/>
-      <c r="AA1" s="55"/>
-      <c r="AB1" s="55"/>
-      <c r="AC1" s="55"/>
-      <c r="AD1" s="55"/>
-      <c r="AE1" s="55"/>
-      <c r="AF1" s="55"/>
-      <c r="AG1" s="55"/>
-      <c r="AH1" s="55"/>
-      <c r="AI1" s="55"/>
-      <c r="AJ1" s="55"/>
-      <c r="AK1" s="55"/>
-      <c r="AL1" s="55"/>
-      <c r="AM1" s="55"/>
-      <c r="AN1" s="3"/>
-      <c r="AO1" s="4"/>
-      <c r="AP1" s="5"/>
-      <c r="AQ1" s="5"/>
-      <c r="AR1" s="5"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="30"/>
     </row>
-    <row r="2" spans="1:44" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6"/>
-      <c r="AL2" s="6"/>
-      <c r="AM2" s="6"/>
-      <c r="AN2" s="8"/>
-      <c r="AO2" s="9"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
-      <c r="AR2" s="5"/>
+    <row r="2" spans="1:34" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="T2" s="5"/>
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="4"/>
+      <c r="AA2" s="4"/>
+      <c r="AB2" s="4"/>
+      <c r="AC2" s="4"/>
+      <c r="AD2" s="4"/>
+      <c r="AE2" s="4"/>
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="4"/>
     </row>
-    <row r="3" spans="1:44" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="11" t="s">
+    <row r="3" spans="1:34" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="33"/>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="9"/>
-      <c r="AA3" s="5"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="5"/>
-      <c r="AD3" s="5"/>
-      <c r="AE3" s="5"/>
-      <c r="AF3" s="5"/>
-      <c r="AG3" s="5"/>
-      <c r="AH3" s="5"/>
-      <c r="AI3" s="5"/>
-      <c r="AJ3" s="12"/>
-      <c r="AK3" s="56" t="s">
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="AA3" s="58"/>
+      <c r="AB3" s="58"/>
+      <c r="AC3" s="58"/>
+      <c r="AD3" s="58"/>
+      <c r="AE3" s="36"/>
+      <c r="AF3" s="36"/>
+      <c r="AG3" s="36"/>
+      <c r="AH3" s="10"/>
+    </row>
+    <row r="4" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="11"/>
+      <c r="N4" s="3"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="12"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="11"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="8"/>
+      <c r="AF4" s="8"/>
+      <c r="AG4" s="13"/>
+      <c r="AH4" s="10"/>
+    </row>
+    <row r="5" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="13"/>
-      <c r="AO3" s="9"/>
-      <c r="AP3" s="5"/>
-      <c r="AQ3" s="5"/>
-      <c r="AR3" s="5"/>
+      <c r="O5" s="38"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="41"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA5" s="38"/>
+      <c r="AB5" s="38"/>
+      <c r="AC5" s="38"/>
+      <c r="AD5" s="38"/>
+      <c r="AE5" s="36"/>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="36"/>
+      <c r="AH5" s="14"/>
     </row>
-    <row r="4" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="15"/>
-      <c r="U4" s="15"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="15"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="10"/>
-      <c r="AI4" s="16"/>
-      <c r="AJ4" s="12"/>
-      <c r="AK4" s="58"/>
-      <c r="AL4" s="58"/>
-      <c r="AM4" s="58"/>
-      <c r="AN4" s="13"/>
-      <c r="AO4" s="9"/>
-      <c r="AP4" s="5"/>
-      <c r="AQ4" s="5"/>
-      <c r="AR4" s="5"/>
+    <row r="6" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="6"/>
     </row>
-    <row r="5" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="52"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="46" t="s">
+    <row r="7" spans="1:34" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+    </row>
+    <row r="8" spans="1:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="54"/>
+      <c r="C8" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="32"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="32"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="32"/>
+    </row>
+    <row r="9" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="55"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="32"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="32"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="32"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="32"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="32"/>
+      <c r="AF9" s="32"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="32"/>
+    </row>
+    <row r="10" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="52"/>
+      <c r="E10" s="21">
+        <v>0</v>
+      </c>
+      <c r="F10" s="22">
+        <v>1</v>
+      </c>
+      <c r="G10" s="22">
+        <v>2</v>
+      </c>
+      <c r="H10" s="22">
         <v>3</v>
       </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="46" t="s">
+      <c r="I10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="32"/>
+      <c r="K10" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="52"/>
+      <c r="M10" s="22">
+        <v>0</v>
+      </c>
+      <c r="N10" s="22">
+        <v>1</v>
+      </c>
+      <c r="O10" s="22">
+        <v>2</v>
+      </c>
+      <c r="P10" s="22">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="22">
         <v>4</v>
       </c>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="17"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="33"/>
-      <c r="AH5" s="33"/>
-      <c r="AI5" s="33"/>
-      <c r="AJ5" s="19"/>
-      <c r="AK5" s="2"/>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="19"/>
-      <c r="AO5" s="9"/>
-      <c r="AP5" s="5"/>
-      <c r="AQ5" s="5"/>
-      <c r="AR5" s="5"/>
+      <c r="R10" s="51" t="s">
+        <v>15</v>
+      </c>
+      <c r="S10" s="52"/>
+      <c r="T10" s="22">
+        <v>0</v>
+      </c>
+      <c r="U10" s="22">
+        <v>1</v>
+      </c>
+      <c r="V10" s="22">
+        <v>2</v>
+      </c>
+      <c r="W10" s="22">
+        <v>3</v>
+      </c>
+      <c r="X10" s="22">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="22">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="22">
+        <v>2</v>
+      </c>
+      <c r="AB10" s="22">
+        <v>3</v>
+      </c>
+      <c r="AC10" s="22">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG10" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH10" s="18" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="6" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="22"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="21"/>
-      <c r="Q6" s="21"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="21"/>
-      <c r="X6" s="21"/>
-      <c r="Y6" s="22"/>
-      <c r="Z6" s="22"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="21"/>
-      <c r="AC6" s="21"/>
-      <c r="AD6" s="21"/>
-      <c r="AE6" s="21"/>
-      <c r="AF6" s="21"/>
-      <c r="AG6" s="22"/>
-      <c r="AH6" s="22"/>
-      <c r="AI6" s="22"/>
-      <c r="AJ6" s="8"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="19"/>
-      <c r="AO6" s="9"/>
-      <c r="AP6" s="5"/>
-      <c r="AQ6" s="5"/>
-      <c r="AR6" s="5"/>
-    </row>
-    <row r="7" spans="1:44" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
-      <c r="Z7" s="10"/>
-      <c r="AA7" s="10"/>
-      <c r="AB7" s="10"/>
-      <c r="AC7" s="10"/>
-      <c r="AD7" s="10"/>
-      <c r="AE7" s="10"/>
-      <c r="AF7" s="10"/>
-      <c r="AG7" s="10"/>
-      <c r="AH7" s="10"/>
-      <c r="AI7" s="10"/>
-      <c r="AJ7" s="10"/>
-      <c r="AK7" s="15"/>
-      <c r="AL7" s="15"/>
-      <c r="AM7" s="15"/>
-      <c r="AN7" s="24"/>
-      <c r="AO7" s="9"/>
-      <c r="AP7" s="5"/>
-      <c r="AQ7" s="5"/>
-      <c r="AR7" s="5"/>
-    </row>
-    <row r="8" spans="1:44" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="43"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="43"/>
-      <c r="Y8" s="43"/>
-      <c r="Z8" s="43"/>
-      <c r="AA8" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB8" s="43"/>
-      <c r="AC8" s="43"/>
-      <c r="AD8" s="43"/>
-      <c r="AE8" s="43"/>
-      <c r="AF8" s="43"/>
-      <c r="AG8" s="43"/>
-      <c r="AH8" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI8" s="43"/>
-      <c r="AJ8" s="43"/>
-      <c r="AK8" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="AL8" s="41"/>
-      <c r="AM8" s="41"/>
-      <c r="AN8" s="41"/>
-      <c r="AO8" s="9"/>
-      <c r="AP8" s="5"/>
-      <c r="AQ8" s="5"/>
-      <c r="AR8" s="5"/>
-    </row>
-    <row r="9" spans="1:44" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="42" t="s">
-        <v>12</v>
-      </c>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="U9" s="43"/>
-      <c r="V9" s="43"/>
-      <c r="W9" s="43"/>
-      <c r="X9" s="43"/>
-      <c r="Y9" s="43"/>
-      <c r="Z9" s="43"/>
-      <c r="AA9" s="43"/>
-      <c r="AB9" s="43"/>
-      <c r="AC9" s="43"/>
-      <c r="AD9" s="43"/>
-      <c r="AE9" s="43"/>
-      <c r="AF9" s="43"/>
-      <c r="AG9" s="43"/>
-      <c r="AH9" s="43"/>
-      <c r="AI9" s="43"/>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="41"/>
-      <c r="AN9" s="41"/>
-      <c r="AO9" s="9"/>
-      <c r="AP9" s="5"/>
-      <c r="AQ9" s="5"/>
-      <c r="AR9" s="5"/>
-    </row>
-    <row r="10" spans="1:44" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="30">
-        <v>0</v>
-      </c>
-      <c r="H10" s="31">
-        <v>1</v>
-      </c>
-      <c r="I10" s="31">
-        <v>2</v>
-      </c>
-      <c r="J10" s="31">
-        <v>3</v>
-      </c>
-      <c r="K10" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="L10" s="43"/>
-      <c r="M10" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="N10" s="45"/>
-      <c r="O10" s="31">
-        <v>0</v>
-      </c>
-      <c r="P10" s="31">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="31">
-        <v>2</v>
-      </c>
-      <c r="R10" s="31">
-        <v>3</v>
-      </c>
-      <c r="S10" s="31">
-        <v>4</v>
-      </c>
-      <c r="T10" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="U10" s="45"/>
-      <c r="V10" s="31">
-        <v>0</v>
-      </c>
-      <c r="W10" s="31">
-        <v>1</v>
-      </c>
-      <c r="X10" s="31">
-        <v>2</v>
-      </c>
-      <c r="Y10" s="31">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="31">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="31">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="31">
-        <v>2</v>
-      </c>
-      <c r="AD10" s="31">
-        <v>3</v>
-      </c>
-      <c r="AE10" s="31">
-        <v>4</v>
-      </c>
-      <c r="AF10" s="42" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG10" s="43"/>
-      <c r="AH10" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI10" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="AJ10" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AK10" s="41"/>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="41"/>
-      <c r="AN10" s="41"/>
-      <c r="AO10" s="9"/>
-      <c r="AP10" s="5"/>
-      <c r="AQ10" s="5"/>
-      <c r="AR10" s="5"/>
-    </row>
-    <row r="11" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -2385,18 +2278,8 @@
       <c r="AF11" s="2"/>
       <c r="AG11" s="2"/>
       <c r="AH11" s="2"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="33"/>
-      <c r="AL11" s="33"/>
-      <c r="AM11" s="33"/>
-      <c r="AN11" s="33"/>
-      <c r="AO11" s="9"/>
-      <c r="AP11" s="5"/>
-      <c r="AQ11" s="5"/>
-      <c r="AR11" s="5"/>
     </row>
-    <row r="12" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -2431,18 +2314,8 @@
       <c r="AF12" s="2"/>
       <c r="AG12" s="2"/>
       <c r="AH12" s="2"/>
-      <c r="AI12" s="2"/>
-      <c r="AJ12" s="2"/>
-      <c r="AK12" s="33"/>
-      <c r="AL12" s="33"/>
-      <c r="AM12" s="33"/>
-      <c r="AN12" s="33"/>
-      <c r="AO12" s="9"/>
-      <c r="AP12" s="5"/>
-      <c r="AQ12" s="5"/>
-      <c r="AR12" s="5"/>
     </row>
-    <row r="13" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -2477,22 +2350,12 @@
       <c r="AF13" s="2"/>
       <c r="AG13" s="2"/>
       <c r="AH13" s="2"/>
-      <c r="AI13" s="2"/>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="33"/>
-      <c r="AL13" s="33"/>
-      <c r="AM13" s="33"/>
-      <c r="AN13" s="33"/>
-      <c r="AO13" s="9"/>
-      <c r="AP13" s="5"/>
-      <c r="AQ13" s="5"/>
-      <c r="AR13" s="5"/>
     </row>
-    <row r="14" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="B14" s="23"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="32"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
@@ -2523,24 +2386,12 @@
       <c r="AF14" s="2"/>
       <c r="AG14" s="2"/>
       <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="AL14" s="41"/>
-      <c r="AM14" s="41"/>
-      <c r="AN14" s="41"/>
-      <c r="AO14" s="9"/>
-      <c r="AP14" s="5"/>
-      <c r="AQ14" s="5"/>
-      <c r="AR14" s="5"/>
     </row>
-    <row r="15" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="23"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="32"/>
+      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
@@ -2571,24 +2422,12 @@
       <c r="AF15" s="2"/>
       <c r="AG15" s="2"/>
       <c r="AH15" s="2"/>
-      <c r="AI15" s="2"/>
-      <c r="AJ15" s="2"/>
-      <c r="AK15" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="AL15" s="33"/>
-      <c r="AM15" s="33"/>
-      <c r="AN15" s="33"/>
-      <c r="AO15" s="9"/>
-      <c r="AP15" s="5"/>
-      <c r="AQ15" s="5"/>
-      <c r="AR15" s="5"/>
     </row>
-    <row r="16" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="B16" s="23"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="32"/>
+      <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -2619,24 +2458,12 @@
       <c r="AF16" s="2"/>
       <c r="AG16" s="2"/>
       <c r="AH16" s="2"/>
-      <c r="AI16" s="2"/>
-      <c r="AJ16" s="2"/>
-      <c r="AK16" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="AL16" s="33"/>
-      <c r="AM16" s="33"/>
-      <c r="AN16" s="33"/>
-      <c r="AO16" s="9"/>
-      <c r="AP16" s="5"/>
-      <c r="AQ16" s="5"/>
-      <c r="AR16" s="5"/>
     </row>
-    <row r="17" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="B17" s="23"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="32"/>
+      <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -2667,24 +2494,12 @@
       <c r="AF17" s="2"/>
       <c r="AG17" s="2"/>
       <c r="AH17" s="2"/>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="AL17" s="33"/>
-      <c r="AM17" s="33"/>
-      <c r="AN17" s="33"/>
-      <c r="AO17" s="9"/>
-      <c r="AP17" s="5"/>
-      <c r="AQ17" s="5"/>
-      <c r="AR17" s="5"/>
     </row>
-    <row r="18" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="B18" s="23"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="32"/>
+      <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -2715,24 +2530,12 @@
       <c r="AF18" s="2"/>
       <c r="AG18" s="2"/>
       <c r="AH18" s="2"/>
-      <c r="AI18" s="2"/>
-      <c r="AJ18" s="2"/>
-      <c r="AK18" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL18" s="33"/>
-      <c r="AM18" s="33"/>
-      <c r="AN18" s="33"/>
-      <c r="AO18" s="9"/>
-      <c r="AP18" s="5"/>
-      <c r="AQ18" s="5"/>
-      <c r="AR18" s="5"/>
     </row>
-    <row r="19" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="B19" s="23"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="32"/>
+      <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -2763,24 +2566,12 @@
       <c r="AF19" s="2"/>
       <c r="AG19" s="2"/>
       <c r="AH19" s="2"/>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL19" s="33"/>
-      <c r="AM19" s="33"/>
-      <c r="AN19" s="33"/>
-      <c r="AO19" s="9"/>
-      <c r="AP19" s="5"/>
-      <c r="AQ19" s="5"/>
-      <c r="AR19" s="5"/>
     </row>
-    <row r="20" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="B20" s="23"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="32"/>
+      <c r="D20" s="2"/>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -2811,24 +2602,12 @@
       <c r="AF20" s="2"/>
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
-      <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="AL20" s="33"/>
-      <c r="AM20" s="33"/>
-      <c r="AN20" s="33"/>
-      <c r="AO20" s="9"/>
-      <c r="AP20" s="5"/>
-      <c r="AQ20" s="5"/>
-      <c r="AR20" s="5"/>
     </row>
-    <row r="21" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="B21" s="23"/>
       <c r="C21" s="2"/>
-      <c r="D21" s="32"/>
+      <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -2859,22 +2638,12 @@
       <c r="AF21" s="2"/>
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
-      <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="33"/>
-      <c r="AL21" s="33"/>
-      <c r="AM21" s="33"/>
-      <c r="AN21" s="33"/>
-      <c r="AO21" s="9"/>
-      <c r="AP21" s="5"/>
-      <c r="AQ21" s="5"/>
-      <c r="AR21" s="5"/>
     </row>
-    <row r="22" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+      <c r="B22" s="23"/>
       <c r="C22" s="2"/>
-      <c r="D22" s="32"/>
+      <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -2905,22 +2674,12 @@
       <c r="AF22" s="2"/>
       <c r="AG22" s="2"/>
       <c r="AH22" s="2"/>
-      <c r="AI22" s="2"/>
-      <c r="AJ22" s="2"/>
-      <c r="AK22" s="33"/>
-      <c r="AL22" s="33"/>
-      <c r="AM22" s="33"/>
-      <c r="AN22" s="33"/>
-      <c r="AO22" s="9"/>
-      <c r="AP22" s="5"/>
-      <c r="AQ22" s="5"/>
-      <c r="AR22" s="5"/>
     </row>
-    <row r="23" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="B23" s="23"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="32"/>
+      <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -2951,22 +2710,12 @@
       <c r="AF23" s="2"/>
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
-      <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="33"/>
-      <c r="AL23" s="33"/>
-      <c r="AM23" s="33"/>
-      <c r="AN23" s="33"/>
-      <c r="AO23" s="9"/>
-      <c r="AP23" s="5"/>
-      <c r="AQ23" s="5"/>
-      <c r="AR23" s="5"/>
     </row>
-    <row r="24" spans="1:44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="B24" s="23"/>
       <c r="C24" s="2"/>
-      <c r="D24" s="32"/>
+      <c r="D24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -2997,24 +2746,14 @@
       <c r="AF24" s="2"/>
       <c r="AG24" s="2"/>
       <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="33"/>
-      <c r="AL24" s="33"/>
-      <c r="AM24" s="33"/>
-      <c r="AN24" s="33"/>
-      <c r="AO24" s="9"/>
-      <c r="AP24" s="5"/>
-      <c r="AQ24" s="5"/>
-      <c r="AR24" s="5"/>
     </row>
-    <row r="25" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="32"/>
+    <row r="25" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="43"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -3045,22 +2784,12 @@
       <c r="AF25" s="2"/>
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
-      <c r="AI25" s="2"/>
-      <c r="AJ25" s="2"/>
-      <c r="AK25" s="33"/>
-      <c r="AL25" s="33"/>
-      <c r="AM25" s="33"/>
-      <c r="AN25" s="33"/>
-      <c r="AO25" s="9"/>
-      <c r="AP25" s="5"/>
-      <c r="AQ25" s="5"/>
-      <c r="AR25" s="5"/>
     </row>
-    <row r="26" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="35"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="32"/>
+    <row r="26" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -3091,114 +2820,75 @@
       <c r="AF26" s="2"/>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
-      <c r="AI26" s="2"/>
-      <c r="AJ26" s="2"/>
-      <c r="AK26" s="33"/>
-      <c r="AL26" s="33"/>
-      <c r="AM26" s="33"/>
-      <c r="AN26" s="33"/>
-      <c r="AO26" s="9"/>
-      <c r="AP26" s="5"/>
-      <c r="AQ26" s="5"/>
-      <c r="AR26" s="5"/>
     </row>
-    <row r="27" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="38"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="59"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="39"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="33"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="33"/>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="33"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="33"/>
-      <c r="AD27" s="33"/>
-      <c r="AE27" s="33"/>
-      <c r="AF27" s="33"/>
-      <c r="AG27" s="33"/>
-      <c r="AH27" s="33"/>
-      <c r="AI27" s="33"/>
-      <c r="AJ27" s="33"/>
-      <c r="AK27" s="2"/>
-      <c r="AL27" s="2"/>
-      <c r="AM27" s="2"/>
-      <c r="AN27" s="2"/>
-      <c r="AO27" s="9"/>
-      <c r="AP27" s="5"/>
-      <c r="AQ27" s="5"/>
-      <c r="AR27" s="5"/>
+    <row r="27" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="47"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="36"/>
+      <c r="Z27" s="36"/>
+      <c r="AA27" s="36"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="36"/>
+      <c r="AD27" s="36"/>
+      <c r="AE27" s="36"/>
+      <c r="AF27" s="36"/>
+      <c r="AG27" s="36"/>
+      <c r="AH27" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="AB5:AF5"/>
-    <mergeCell ref="AG5:AI5"/>
-    <mergeCell ref="A8:D9"/>
-    <mergeCell ref="E8:L9"/>
-    <mergeCell ref="M8:Z8"/>
-    <mergeCell ref="AA8:AG9"/>
-    <mergeCell ref="AH8:AJ9"/>
-    <mergeCell ref="A1:C5"/>
-    <mergeCell ref="D1:AM1"/>
-    <mergeCell ref="F3:O3"/>
-    <mergeCell ref="Q3:Y3"/>
-    <mergeCell ref="AK3:AM4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="AK13:AL13"/>
-    <mergeCell ref="AM13:AN13"/>
-    <mergeCell ref="AK8:AN10"/>
-    <mergeCell ref="M9:S9"/>
-    <mergeCell ref="T9:Z9"/>
-    <mergeCell ref="E10:F10"/>
+  <mergeCells count="28">
+    <mergeCell ref="Y27:AE27"/>
+    <mergeCell ref="AF27:AH27"/>
+    <mergeCell ref="P5:S5"/>
+    <mergeCell ref="A25:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:J27"/>
+    <mergeCell ref="K27:Q27"/>
+    <mergeCell ref="R27:X27"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="I10:J10"/>
     <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="T10:U10"/>
-    <mergeCell ref="AF10:AG10"/>
-    <mergeCell ref="AK11:AN11"/>
-    <mergeCell ref="AK12:AL12"/>
-    <mergeCell ref="AM12:AN12"/>
-    <mergeCell ref="AK14:AN14"/>
-    <mergeCell ref="AL15:AN15"/>
-    <mergeCell ref="AL16:AN16"/>
-    <mergeCell ref="AL17:AN17"/>
-    <mergeCell ref="AL18:AN18"/>
-    <mergeCell ref="AL19:AN19"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:L27"/>
-    <mergeCell ref="AL20:AN20"/>
-    <mergeCell ref="AK21:AN21"/>
-    <mergeCell ref="AK22:AN23"/>
-    <mergeCell ref="M27:S27"/>
-    <mergeCell ref="T27:Z27"/>
-    <mergeCell ref="AA27:AG27"/>
-    <mergeCell ref="AH27:AJ27"/>
-    <mergeCell ref="AK24:AN24"/>
-    <mergeCell ref="A25:C26"/>
-    <mergeCell ref="AK25:AN25"/>
-    <mergeCell ref="AK26:AN26"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="AD10:AE10"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="C8:J9"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="Y8:AE9"/>
+    <mergeCell ref="AF8:AH9"/>
+    <mergeCell ref="K9:Q9"/>
+    <mergeCell ref="R9:X9"/>
+    <mergeCell ref="D3:M3"/>
+    <mergeCell ref="O3:W3"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="Z5:AD5"/>
+    <mergeCell ref="AE5:AG5"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="Z3:AD3"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.19645699999999999" top="0.91063000000000005" bottom="0.96535400000000005" header="0.429921" footer="0.67007899999999998"/>
   <pageSetup pageOrder="overThenDown" orientation="landscape"/>
@@ -3206,6 +2896,5 @@
     <oddHeader>&amp;C&amp;"Arial,Regular"&amp;14&amp;K000000CURSO NACIONAL DE ENTRENADORES NIVEL I</oddHeader>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/proyFinal/src/datos/plantilla_de_estadisticas.xlsx
+++ b/proyFinal/src/datos/plantilla_de_estadisticas.xlsx
@@ -1,31 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizas\proyectoFinal\proyFinal\src\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lizas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37030658-F1C8-4286-80F4-ABD091347062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C188D732-FF20-4E90-86AB-B7A3E568D2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-1728" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t>ESTADISTICA INDIVIDUAL DE JUEGO</t>
   </si>
   <si>
     <t>vs</t>
+  </si>
+  <si>
+    <t>PARTIDO</t>
   </si>
   <si>
     <t>FECHA</t>
@@ -67,9 +83,6 @@
     <t>0                           E            B</t>
   </si>
   <si>
-    <t>0                     E            B</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -81,23 +94,14 @@
   <si>
     <t xml:space="preserve"> OBSERVACIONES</t>
   </si>
-  <si>
-    <t>PARTIDO</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
@@ -123,6 +127,41 @@
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -138,7 +177,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -147,29 +186,40 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -181,10 +231,10 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
@@ -193,41 +243,115 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
         <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="10"/>
       </top>
@@ -241,10 +365,10 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
@@ -253,13 +377,13 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
         <color indexed="10"/>
@@ -298,14 +422,45 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="10"/>
-      </top>
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
@@ -319,70 +474,11 @@
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -392,74 +488,202 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="10"/>
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
       </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="10"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="10"/>
       </top>
@@ -473,12 +697,14 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -486,185 +712,223 @@
         <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="10"/>
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{EA5B43E5-26B1-48A7-967A-6D050EDC4241}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
@@ -1792,247 +2056,270 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.75" defaultRowHeight="14.65" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AJ26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="14.7" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.875" style="1" customWidth="1"/>
-    <col min="3" max="33" width="3.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.8984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.8984375" style="1" customWidth="1"/>
+    <col min="3" max="8" width="3.3984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.09765625" style="1" customWidth="1"/>
+    <col min="10" max="16" width="3.3984375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="6.09765625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.59765625" style="1" customWidth="1"/>
+    <col min="19" max="24" width="3.3984375" style="1" customWidth="1"/>
+    <col min="25" max="25" width="5.5" style="1" customWidth="1"/>
+    <col min="26" max="26" width="5.3984375" style="1" customWidth="1"/>
+    <col min="27" max="30" width="3.3984375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="7.09765625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="5" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.3984375" style="1" customWidth="1"/>
     <col min="34" max="34" width="4" style="1" customWidth="1"/>
-    <col min="35" max="35" width="10.75" style="1" customWidth="1"/>
-    <col min="36" max="16384" width="10.75" style="1"/>
+    <col min="35" max="35" width="10.8984375" style="1" customWidth="1"/>
+    <col min="36" max="16384" width="10.8984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="30"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
+      <c r="Y1" s="81"/>
+      <c r="Z1" s="81"/>
+      <c r="AA1" s="81"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="81"/>
+      <c r="AF1" s="81"/>
+      <c r="AG1" s="81"/>
+      <c r="AH1" s="81"/>
+      <c r="AI1" s="63"/>
+      <c r="AJ1" s="48"/>
     </row>
-    <row r="2" spans="1:34" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
+    <row r="2" spans="1:36" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="50"/>
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="50"/>
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="50"/>
+      <c r="AE2" s="52"/>
+      <c r="AF2" s="52"/>
+      <c r="AG2" s="52"/>
+      <c r="AH2" s="57"/>
+      <c r="AI2" s="46"/>
+      <c r="AJ2" s="38"/>
     </row>
-    <row r="3" spans="1:34" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="9" t="s">
+    <row r="3" spans="1:36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="73"/>
+      <c r="N3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="O3" s="36"/>
-      <c r="P3" s="36"/>
-      <c r="Q3" s="36"/>
-      <c r="R3" s="36"/>
-      <c r="S3" s="36"/>
-      <c r="T3" s="36"/>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="36"/>
+      <c r="O3" s="70"/>
+      <c r="P3" s="71"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="74"/>
+      <c r="W3" s="75"/>
       <c r="X3" s="7"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="57" t="s">
-        <v>20</v>
-      </c>
-      <c r="AA3" s="58"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="58"/>
-      <c r="AD3" s="58"/>
-      <c r="AE3" s="36"/>
-      <c r="AF3" s="36"/>
-      <c r="AG3" s="36"/>
-      <c r="AH3" s="10"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="83"/>
+      <c r="AB3" s="84"/>
+      <c r="AC3" s="84"/>
+      <c r="AD3" s="84"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="86"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="58"/>
+      <c r="AI3" s="46"/>
+      <c r="AJ3" s="38"/>
     </row>
-    <row r="4" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="26"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12"/>
-      <c r="S4" s="12"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-      <c r="AA4" s="3"/>
-      <c r="AB4" s="3"/>
-      <c r="AC4" s="3"/>
-      <c r="AD4" s="3"/>
-      <c r="AE4" s="8"/>
-      <c r="AF4" s="8"/>
-      <c r="AG4" s="13"/>
-      <c r="AH4" s="10"/>
+    <row r="4" spans="1:36" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="8"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="35"/>
+      <c r="AF4" s="35"/>
+      <c r="AG4" s="36"/>
+      <c r="AH4" s="59"/>
+      <c r="AI4" s="46"/>
+      <c r="AJ4" s="38"/>
     </row>
-    <row r="5" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="37" t="s">
-        <v>2</v>
-      </c>
-      <c r="O5" s="38"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="41"/>
+    <row r="5" spans="1:36" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="82" t="s">
+        <v>3</v>
+      </c>
+      <c r="O5" s="88"/>
+      <c r="P5" s="98"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="72"/>
+      <c r="S5" s="73"/>
       <c r="T5" s="7"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="37" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA5" s="38"/>
-      <c r="AB5" s="38"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="38"/>
-      <c r="AE5" s="36"/>
-      <c r="AF5" s="36"/>
-      <c r="AG5" s="36"/>
-      <c r="AH5" s="14"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="82" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA5" s="83"/>
+      <c r="AB5" s="84"/>
+      <c r="AC5" s="84"/>
+      <c r="AD5" s="84"/>
+      <c r="AE5" s="92"/>
+      <c r="AF5" s="93"/>
+      <c r="AG5" s="94"/>
+      <c r="AH5" s="60"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="38"/>
     </row>
-    <row r="6" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="15"/>
-      <c r="O6" s="15"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="15"/>
-      <c r="V6" s="15"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="15"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="15"/>
-      <c r="AA6" s="15"/>
-      <c r="AB6" s="15"/>
-      <c r="AC6" s="15"/>
-      <c r="AD6" s="15"/>
-      <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="6"/>
+    <row r="6" spans="1:36" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="12"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="12"/>
+      <c r="X6" s="12"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="12"/>
+      <c r="AA6" s="12"/>
+      <c r="AB6" s="12"/>
+      <c r="AC6" s="12"/>
+      <c r="AD6" s="12"/>
+      <c r="AE6" s="37"/>
+      <c r="AF6" s="37"/>
+      <c r="AG6" s="37"/>
+      <c r="AH6" s="61"/>
+      <c r="AI6" s="46"/>
+      <c r="AJ6" s="46"/>
     </row>
-    <row r="7" spans="1:34" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+    <row r="7" spans="1:36" ht="8.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="27"/>
       <c r="D7" s="27"/>
       <c r="E7" s="27"/>
       <c r="F7" s="27"/>
@@ -2042,853 +2329,825 @@
       <c r="J7" s="27"/>
       <c r="K7" s="27"/>
       <c r="L7" s="27"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="8"/>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="8"/>
-      <c r="AH7" s="8"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27"/>
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="27"/>
+      <c r="AC7" s="27"/>
+      <c r="AD7" s="27"/>
+      <c r="AE7" s="27"/>
+      <c r="AF7" s="27"/>
+      <c r="AG7" s="27"/>
+      <c r="AH7" s="62"/>
+      <c r="AI7" s="38"/>
+      <c r="AJ7" s="38"/>
     </row>
-    <row r="8" spans="1:34" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
+    <row r="8" spans="1:36" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="96"/>
+      <c r="C8" s="76" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="76"/>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="76"/>
+      <c r="S8" s="76"/>
+      <c r="T8" s="76"/>
+      <c r="U8" s="76"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="76"/>
+      <c r="X8" s="76"/>
+      <c r="Y8" s="76"/>
+      <c r="Z8" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="69"/>
+      <c r="AB8" s="69"/>
+      <c r="AC8" s="69"/>
+      <c r="AD8" s="69"/>
+      <c r="AE8" s="69"/>
+      <c r="AF8" s="77" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG8" s="77"/>
+      <c r="AH8" s="77"/>
+      <c r="AI8" s="47"/>
+      <c r="AJ8" s="47"/>
+    </row>
+    <row r="9" spans="1:36" ht="14.7" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="83"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="77" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+      <c r="O9" s="77"/>
+      <c r="P9" s="77"/>
+      <c r="Q9" s="77"/>
+      <c r="R9" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="S9" s="77"/>
+      <c r="T9" s="77"/>
+      <c r="U9" s="77"/>
+      <c r="V9" s="77"/>
+      <c r="W9" s="77"/>
+      <c r="X9" s="77"/>
+      <c r="Y9" s="77"/>
+      <c r="Z9" s="69"/>
+      <c r="AA9" s="69"/>
+      <c r="AB9" s="69"/>
+      <c r="AC9" s="69"/>
+      <c r="AD9" s="69"/>
+      <c r="AE9" s="69"/>
+      <c r="AF9" s="77"/>
+      <c r="AG9" s="77"/>
+      <c r="AH9" s="77"/>
+      <c r="AI9" s="47"/>
+      <c r="AJ9" s="47"/>
+    </row>
+    <row r="10" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="80"/>
+      <c r="E10" s="42">
+        <v>0</v>
+      </c>
+      <c r="F10" s="28">
+        <v>1</v>
+      </c>
+      <c r="G10" s="28">
+        <v>2</v>
+      </c>
+      <c r="H10" s="28">
+        <v>3</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="80"/>
+      <c r="L10" s="28">
+        <v>0</v>
+      </c>
+      <c r="M10" s="28">
+        <v>1</v>
+      </c>
+      <c r="N10" s="28">
+        <v>2</v>
+      </c>
+      <c r="O10" s="28">
+        <v>3</v>
+      </c>
+      <c r="P10" s="30">
         <v>4</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="35"/>
-      <c r="Y8" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z8" s="32"/>
-      <c r="AA8" s="32"/>
-      <c r="AB8" s="32"/>
-      <c r="AC8" s="32"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="32"/>
-      <c r="AF8" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG8" s="32"/>
-      <c r="AH8" s="32"/>
+      <c r="Q10" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="R10" s="79" t="s">
+        <v>15</v>
+      </c>
+      <c r="S10" s="80"/>
+      <c r="T10" s="28">
+        <v>0</v>
+      </c>
+      <c r="U10" s="28">
+        <v>1</v>
+      </c>
+      <c r="V10" s="28">
+        <v>2</v>
+      </c>
+      <c r="W10" s="28">
+        <v>3</v>
+      </c>
+      <c r="X10" s="30">
+        <v>4</v>
+      </c>
+      <c r="Y10" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z10" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="28">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="28">
+        <v>2</v>
+      </c>
+      <c r="AC10" s="28">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="30">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF10" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG10" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH10" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI10" s="64"/>
     </row>
-    <row r="9" spans="1:34" ht="14.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="55"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="32"/>
-      <c r="R9" s="31" t="s">
-        <v>10</v>
-      </c>
-      <c r="S9" s="32"/>
-      <c r="T9" s="32"/>
-      <c r="U9" s="32"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="32"/>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="32"/>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="32"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="32"/>
-      <c r="AG9" s="32"/>
-      <c r="AH9" s="32"/>
+    <row r="11" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="66"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="F11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="66"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="66"/>
+      <c r="M11" s="66"/>
+      <c r="N11" s="66"/>
+      <c r="O11" s="66"/>
+      <c r="P11" s="66"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="66"/>
+      <c r="U11" s="66"/>
+      <c r="V11" s="66"/>
+      <c r="W11" s="66"/>
+      <c r="X11" s="66"/>
+      <c r="Y11" s="34"/>
+      <c r="Z11" s="66"/>
+      <c r="AA11" s="66"/>
+      <c r="AB11" s="66"/>
+      <c r="AC11" s="66"/>
+      <c r="AD11" s="66"/>
+      <c r="AE11" s="34"/>
+      <c r="AF11" s="65"/>
+      <c r="AG11" s="65"/>
+      <c r="AH11" s="34"/>
+      <c r="AI11" s="64"/>
     </row>
-    <row r="10" spans="1:34" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="21">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22">
-        <v>1</v>
-      </c>
-      <c r="G10" s="22">
-        <v>2</v>
-      </c>
-      <c r="H10" s="22">
-        <v>3</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="51" t="s">
+    <row r="12" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="34"/>
+      <c r="Z12" s="5"/>
+      <c r="AA12" s="20"/>
+      <c r="AB12" s="20"/>
+      <c r="AC12" s="20"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="34"/>
+      <c r="AF12" s="40"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="39"/>
+    </row>
+    <row r="13" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="34"/>
+      <c r="Z13" s="5"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="34"/>
+      <c r="AF13" s="24"/>
+      <c r="AG13" s="32"/>
+      <c r="AH13" s="32"/>
+    </row>
+    <row r="14" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="20"/>
+      <c r="N14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="5"/>
+      <c r="AA14" s="20"/>
+      <c r="AB14" s="20"/>
+      <c r="AC14" s="20"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="34"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="20"/>
+      <c r="AH14" s="20"/>
+    </row>
+    <row r="15" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="20"/>
+      <c r="N15" s="20"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="20"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="34"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="20"/>
+      <c r="AB15" s="20"/>
+      <c r="AC15" s="20"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="34"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="20"/>
+      <c r="AH15" s="20"/>
+    </row>
+    <row r="16" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="20"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="34"/>
+      <c r="Z16" s="5"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="4"/>
+      <c r="AE16" s="34"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="20"/>
+      <c r="AH16" s="20"/>
+    </row>
+    <row r="17" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="34"/>
+      <c r="Z17" s="5"/>
+      <c r="AA17" s="20"/>
+      <c r="AB17" s="20"/>
+      <c r="AC17" s="20"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="34"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="20"/>
+      <c r="AH17" s="20"/>
+    </row>
+    <row r="18" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="20"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="34"/>
+      <c r="Z18" s="5"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="34"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="20"/>
+    </row>
+    <row r="19" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="20"/>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="20"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="34"/>
+      <c r="Z19" s="5"/>
+      <c r="AA19" s="20"/>
+      <c r="AB19" s="20"/>
+      <c r="AC19" s="20"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="34"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="20"/>
+      <c r="AH19" s="20"/>
+    </row>
+    <row r="20" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="20"/>
+      <c r="Q20" s="20"/>
+      <c r="R20" s="20"/>
+      <c r="S20" s="20"/>
+      <c r="T20" s="20"/>
+      <c r="U20" s="20"/>
+      <c r="V20" s="20"/>
+      <c r="W20" s="20"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20" s="5"/>
+      <c r="AA20" s="20"/>
+      <c r="AB20" s="20"/>
+      <c r="AC20" s="20"/>
+      <c r="AD20" s="4"/>
+      <c r="AE20" s="34"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="20"/>
+      <c r="AH20" s="20"/>
+    </row>
+    <row r="21" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="20"/>
+      <c r="O21" s="20"/>
+      <c r="P21" s="20"/>
+      <c r="Q21" s="20"/>
+      <c r="R21" s="20"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="34"/>
+      <c r="Z21" s="5"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="34"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="20"/>
+      <c r="AH21" s="20"/>
+    </row>
+    <row r="22" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="20"/>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="5"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="20"/>
+      <c r="AH22" s="20"/>
+    </row>
+    <row r="23" spans="1:36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="34"/>
+      <c r="Z23" s="5"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="4"/>
+      <c r="AE23" s="34"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="20"/>
+      <c r="AH23" s="20"/>
+    </row>
+    <row r="24" spans="1:36" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="20"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="17"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="16"/>
+      <c r="AE24" s="34"/>
+      <c r="AF24" s="23"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+    </row>
+    <row r="25" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="67" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="52"/>
-      <c r="M10" s="22">
-        <v>0</v>
-      </c>
-      <c r="N10" s="22">
-        <v>1</v>
-      </c>
-      <c r="O10" s="22">
-        <v>2</v>
-      </c>
-      <c r="P10" s="22">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="22">
-        <v>4</v>
-      </c>
-      <c r="R10" s="51" t="s">
-        <v>15</v>
-      </c>
-      <c r="S10" s="52"/>
-      <c r="T10" s="22">
-        <v>0</v>
-      </c>
-      <c r="U10" s="22">
-        <v>1</v>
-      </c>
-      <c r="V10" s="22">
-        <v>2</v>
-      </c>
-      <c r="W10" s="22">
-        <v>3</v>
-      </c>
-      <c r="X10" s="22">
-        <v>4</v>
-      </c>
-      <c r="Y10" s="22">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="22">
-        <v>2</v>
-      </c>
-      <c r="AB10" s="22">
-        <v>3</v>
-      </c>
-      <c r="AC10" s="22">
-        <v>4</v>
-      </c>
-      <c r="AD10" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG10" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH10" s="18" t="s">
-        <v>18</v>
-      </c>
+      <c r="B25" s="68"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="41"/>
+      <c r="J25" s="53"/>
+      <c r="K25" s="53"/>
+      <c r="L25" s="53"/>
+      <c r="M25" s="53"/>
+      <c r="N25" s="53"/>
+      <c r="O25" s="53"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="53"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="54"/>
+      <c r="T25" s="54"/>
+      <c r="U25" s="54"/>
+      <c r="V25" s="54"/>
+      <c r="W25" s="54"/>
+      <c r="X25" s="54"/>
+      <c r="Y25" s="53"/>
+      <c r="Z25" s="53"/>
+      <c r="AA25" s="53"/>
+      <c r="AB25" s="53"/>
+      <c r="AC25" s="53"/>
+      <c r="AD25" s="55"/>
+      <c r="AE25" s="41"/>
+      <c r="AF25" s="56"/>
+      <c r="AG25" s="53"/>
+      <c r="AH25" s="41"/>
     </row>
-    <row r="11" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
-      <c r="AG11" s="2"/>
-      <c r="AH11" s="2"/>
-    </row>
-    <row r="12" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2"/>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2"/>
-      <c r="AG12" s="2"/>
-      <c r="AH12" s="2"/>
-    </row>
-    <row r="13" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2"/>
-      <c r="AE13" s="2"/>
-      <c r="AF13" s="2"/>
-      <c r="AG13" s="2"/>
-      <c r="AH13" s="2"/>
-    </row>
-    <row r="14" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AH14" s="2"/>
-    </row>
-    <row r="15" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="2"/>
-      <c r="AD15" s="2"/>
-      <c r="AE15" s="2"/>
-      <c r="AF15" s="2"/>
-      <c r="AG15" s="2"/>
-      <c r="AH15" s="2"/>
-    </row>
-    <row r="16" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="2"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="2"/>
-      <c r="AE16" s="2"/>
-      <c r="AF16" s="2"/>
-      <c r="AG16" s="2"/>
-      <c r="AH16" s="2"/>
-    </row>
-    <row r="17" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2"/>
-      <c r="AE17" s="2"/>
-      <c r="AF17" s="2"/>
-      <c r="AG17" s="2"/>
-      <c r="AH17" s="2"/>
-    </row>
-    <row r="18" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
-      <c r="AD18" s="2"/>
-      <c r="AE18" s="2"/>
-      <c r="AF18" s="2"/>
-      <c r="AG18" s="2"/>
-      <c r="AH18" s="2"/>
-    </row>
-    <row r="19" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
-      <c r="AH19" s="2"/>
-    </row>
-    <row r="20" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
-      <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="2"/>
-      <c r="AG20" s="2"/>
-      <c r="AH20" s="2"/>
-    </row>
-    <row r="21" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
-      <c r="AG21" s="2"/>
-      <c r="AH21" s="2"/>
-    </row>
-    <row r="22" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-      <c r="AC22" s="2"/>
-      <c r="AD22" s="2"/>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="2"/>
-      <c r="AG22" s="2"/>
-      <c r="AH22" s="2"/>
-    </row>
-    <row r="23" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
-      <c r="AC23" s="2"/>
-      <c r="AD23" s="2"/>
-      <c r="AE23" s="2"/>
-      <c r="AF23" s="2"/>
-      <c r="AG23" s="2"/>
-      <c r="AH23" s="2"/>
-    </row>
-    <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-    </row>
-    <row r="25" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="2"/>
-      <c r="AD25" s="2"/>
-      <c r="AE25" s="2"/>
-      <c r="AF25" s="2"/>
-      <c r="AG25" s="2"/>
-      <c r="AH25" s="2"/>
-    </row>
-    <row r="26" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="2"/>
-      <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
-      <c r="AC26" s="2"/>
-      <c r="AD26" s="2"/>
-      <c r="AE26" s="2"/>
-      <c r="AF26" s="2"/>
-      <c r="AG26" s="2"/>
-      <c r="AH26" s="2"/>
-    </row>
-    <row r="27" spans="1:34" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="46" t="s">
+    <row r="26" spans="1:36" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="49"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="36"/>
-      <c r="R27" s="36"/>
-      <c r="S27" s="36"/>
-      <c r="T27" s="36"/>
-      <c r="U27" s="36"/>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="36"/>
-      <c r="Y27" s="36"/>
-      <c r="Z27" s="36"/>
-      <c r="AA27" s="36"/>
-      <c r="AB27" s="36"/>
-      <c r="AC27" s="36"/>
-      <c r="AD27" s="36"/>
-      <c r="AE27" s="36"/>
-      <c r="AF27" s="36"/>
-      <c r="AG27" s="36"/>
-      <c r="AH27" s="36"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="78"/>
+      <c r="D26" s="78"/>
+      <c r="E26" s="78"/>
+      <c r="F26" s="78"/>
+      <c r="G26" s="78"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="78"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="78"/>
+      <c r="M26" s="78"/>
+      <c r="N26" s="78"/>
+      <c r="O26" s="78"/>
+      <c r="P26" s="78"/>
+      <c r="Q26" s="78"/>
+      <c r="R26" s="78"/>
+      <c r="S26" s="78"/>
+      <c r="T26" s="78"/>
+      <c r="U26" s="78"/>
+      <c r="V26" s="78"/>
+      <c r="W26" s="78"/>
+      <c r="X26" s="78"/>
+      <c r="Y26" s="78"/>
+      <c r="Z26" s="78"/>
+      <c r="AA26" s="78"/>
+      <c r="AB26" s="78"/>
+      <c r="AC26" s="78"/>
+      <c r="AD26" s="78"/>
+      <c r="AE26" s="78"/>
+      <c r="AF26" s="78"/>
+      <c r="AG26" s="78"/>
+      <c r="AH26" s="78"/>
+      <c r="AI26" s="38"/>
+      <c r="AJ26" s="38"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="Y27:AE27"/>
-    <mergeCell ref="AF27:AH27"/>
+  <mergeCells count="22">
+    <mergeCell ref="C26:AH26"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="A1:AH1"/>
+    <mergeCell ref="Z5:AD5"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AF8:AH9"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="Z3:AD3"/>
+    <mergeCell ref="AE5:AG5"/>
+    <mergeCell ref="A8:B9"/>
     <mergeCell ref="P5:S5"/>
-    <mergeCell ref="A25:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:J27"/>
-    <mergeCell ref="K27:Q27"/>
-    <mergeCell ref="R27:X27"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="AD10:AE10"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="A1:AH1"/>
-    <mergeCell ref="C8:J9"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="Y8:AE9"/>
-    <mergeCell ref="AF8:AH9"/>
-    <mergeCell ref="K9:Q9"/>
-    <mergeCell ref="R9:X9"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="Z8:AE9"/>
     <mergeCell ref="D3:M3"/>
     <mergeCell ref="O3:W3"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="Z5:AD5"/>
-    <mergeCell ref="AE5:AG5"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="Z3:AD3"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="J9:Q9"/>
+    <mergeCell ref="R9:Y9"/>
+    <mergeCell ref="J8:Y8"/>
   </mergeCells>
   <pageMargins left="0.35" right="0.19645699999999999" top="0.91063000000000005" bottom="0.96535400000000005" header="0.429921" footer="0.67007899999999998"/>
   <pageSetup pageOrder="overThenDown" orientation="landscape"/>
